--- a/scripts/templates/cdisc_sdtm_dataset_specializations_latest_template.xlsx
+++ b/scripts/templates/cdisc_sdtm_dataset_specializations_latest_template.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_github\cdisc-org\COSMoS\scripts\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE3D43AA-D5C3-4499-896E-3ABCA91110C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB28C90-AEA4-4C12-B317-8B7397FD879A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="1" r:id="rId1"/>
     <sheet name="SDTM Dataset Specializations" sheetId="2" r:id="rId2"/>
-    <sheet name="Domains" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SDTM Dataset Specializations'!$A$1:$AF$1</definedName>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="76">
   <si>
     <t>Group</t>
   </si>
@@ -403,7 +402,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -417,9 +416,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -611,12 +607,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -633,7 +629,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -642,82 +638,82 @@
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="11"/>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="11"/>
+      <c r="D5" s="10"/>
     </row>
     <row r="6" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="11"/>
+      <c r="D6" s="10"/>
     </row>
     <row r="7" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="10"/>
     </row>
     <row r="8" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
+      <c r="A10" s="9"/>
       <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -726,98 +722,98 @@
       <c r="C11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="10"/>
     </row>
     <row r="13" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="10"/>
+      <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11"/>
+      <c r="A17" s="10"/>
       <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="10"/>
+      <c r="D17" s="9"/>
     </row>
     <row r="18" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11"/>
+      <c r="A18" s="10"/>
       <c r="B18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11"/>
+      <c r="A19" s="10"/>
       <c r="B19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="10"/>
+      <c r="D19" s="9"/>
     </row>
     <row r="20" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11"/>
+      <c r="A20" s="10"/>
       <c r="B20" s="2" t="s">
         <v>44</v>
       </c>
@@ -829,148 +825,148 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11"/>
+      <c r="A21" s="10"/>
       <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11"/>
+      <c r="A22" s="10"/>
       <c r="B22" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="11"/>
+      <c r="A23" s="10"/>
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="11"/>
+      <c r="A24" s="10"/>
       <c r="B24" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="10"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="11"/>
+      <c r="A25" s="10"/>
       <c r="B25" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="11"/>
+      <c r="A26" s="10"/>
       <c r="B26" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="10"/>
     </row>
     <row r="27" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="11"/>
+      <c r="A27" s="10"/>
       <c r="B27" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="11"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="11"/>
+      <c r="A28" s="10"/>
       <c r="B28" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="11"/>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="11"/>
+      <c r="A29" s="10"/>
       <c r="B29" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="11"/>
+      <c r="D29" s="10"/>
     </row>
     <row r="30" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11"/>
+      <c r="A30" s="10"/>
       <c r="B30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="11"/>
+      <c r="D30" s="10"/>
     </row>
     <row r="31" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11"/>
+      <c r="A31" s="10"/>
       <c r="B31" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D31" s="11"/>
+      <c r="D31" s="10"/>
     </row>
     <row r="32" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="11"/>
+      <c r="A32" s="10"/>
       <c r="B32" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="11"/>
+      <c r="D32" s="10"/>
     </row>
     <row r="33" spans="1:4" ht="29.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
+      <c r="A33" s="10"/>
       <c r="B33" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="11"/>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" spans="1:4" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10"/>
+      <c r="A34" s="9"/>
       <c r="B34" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="10"/>
+      <c r="D34" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1130,22 +1126,4 @@
   <pageMargins left="0.05" right="0.05" top="0.5" bottom="0.5" header="0" footer="0"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D4D58F-1B91-4026-A7FA-AD7CF788CB4A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>